--- a/sources/heihachi_step6b.xlsx
+++ b/sources/heihachi_step6b.xlsx
@@ -423,7 +423,7 @@
     <col width="25" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
     <col width="7" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
@@ -2661,12 +2661,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>– ~1+2 [~u_~d]</t>
+          <t>– ~1+2</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>– Demon Executioner [SS]</t>
+          <t>– Demon Executioner</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>(~u)SS; (~d)SS</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">

--- a/sources/heihachi_step6b.xlsx
+++ b/sources/heihachi_step6b.xlsx
@@ -790,6 +790,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>f46ce297-20aa-42e9-8fad-54b3f4704d3d</t>
+        </is>
+      </c>
       <c r="R7" t="inlineStr">
         <is>
           <t>f46ce297-20aa-42e9-8fad-54b3f4704d3d</t>
@@ -837,6 +842,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>2bed6e68-3dcb-46ce-8b44-5a8ab9825180</t>
+        </is>
+      </c>
       <c r="R8" t="inlineStr">
         <is>
           <t>2bed6e68-3dcb-46ce-8b44-5a8ab9825180</t>
@@ -882,6 +892,11 @@
       <c r="M9" t="inlineStr">
         <is>
           <t>None</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>94e89bd5-df08-4d1f-954d-ff55d170def7</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -5420,6 +5435,11 @@
           <t>mhhLLmhhmm</t>
         </is>
       </c>
+      <c r="Q94" t="inlineStr">
+        <is>
+          <t>5e401bff-867a-4231-89fe-31140fb8cfa3</t>
+        </is>
+      </c>
       <c r="R94" t="inlineStr">
         <is>
           <t>5e401bff-867a-4231-89fe-31140fb8cfa3</t>
@@ -5452,6 +5472,11 @@
           <t>mhhLLmhhmm</t>
         </is>
       </c>
+      <c r="Q95" t="inlineStr">
+        <is>
+          <t>4843994c-4a83-4e19-a59d-b3e33a4b6216</t>
+        </is>
+      </c>
       <c r="R95" t="inlineStr">
         <is>
           <t>4843994c-4a83-4e19-a59d-b3e33a4b6216</t>
@@ -5484,6 +5509,11 @@
           <t>mhhLLmhmmm</t>
         </is>
       </c>
+      <c r="Q96" t="inlineStr">
+        <is>
+          <t>b75ce8db-3ddd-40cc-b908-e15c334e3eff</t>
+        </is>
+      </c>
       <c r="R96" t="inlineStr">
         <is>
           <t>b75ce8db-3ddd-40cc-b908-e15c334e3eff</t>
@@ -5514,6 +5544,11 @@
       <c r="K97" t="inlineStr">
         <is>
           <t>hhhhmmlhmm</t>
+        </is>
+      </c>
+      <c r="Q97" t="inlineStr">
+        <is>
+          <t>59b8bd40-2cec-44af-a5be-02b8f9c50b3c</t>
         </is>
       </c>
       <c r="R97" t="inlineStr">
